--- a/registration_forms/033_returning_user_registration--registration_forms.xlsx
+++ b/registration_forms/033_returning_user_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -822,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>british_columbia</t>
+          <t>manitoba</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>British Columbia</t>
+          <t>Manitoba</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>manitoba</t>
+          <t>new_brunswick</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Manitoba</t>
+          <t>New Brunswick</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>new_brunswick</t>
+          <t>ontario</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New Brunswick</t>
+          <t>Ontario</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ontario</t>
+          <t>quebec</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ontario</t>
+          <t>Quebec</t>
         </is>
       </c>
     </row>
@@ -2028,29 +2028,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>quebec</t>
+          <t>saskatchewan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Quebec</t>
+          <t>Saskatchewan</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>user_state_choices</t>
+          <t>user_agreement_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>saskatchewan</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saskatchewan</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2062,27 +2062,10 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>user_agreement_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
         <is>
           <t>No</t>
         </is>
